--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291569</v>
+        <v>122291581</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498385</v>
+        <v>498055</v>
       </c>
       <c r="R2" t="n">
-        <v>7070568</v>
+        <v>7070278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291578</v>
+        <v>122291576</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498060</v>
+        <v>498249</v>
       </c>
       <c r="R3" t="n">
-        <v>7070363</v>
+        <v>7070325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291579</v>
+        <v>122291578</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -932,7 +932,7 @@
         <v>498060</v>
       </c>
       <c r="R4" t="n">
-        <v>7070326</v>
+        <v>7070363</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291575</v>
+        <v>122291571</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498330</v>
+        <v>498388</v>
       </c>
       <c r="R5" t="n">
         <v>7070466</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291563</v>
+        <v>122291582</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497800</v>
+        <v>498057</v>
       </c>
       <c r="R6" t="n">
-        <v>7070212</v>
+        <v>7070278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291565</v>
+        <v>122291568</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498003</v>
+        <v>498247</v>
       </c>
       <c r="R7" t="n">
-        <v>7070188</v>
+        <v>7070260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291571</v>
+        <v>122291564</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498388</v>
+        <v>497847</v>
       </c>
       <c r="R8" t="n">
-        <v>7070466</v>
+        <v>7070241</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291584</v>
+        <v>122291583</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1457,37 +1457,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497959</v>
+        <v>498056</v>
       </c>
       <c r="R9" t="n">
-        <v>7070233</v>
+        <v>7070237</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291583</v>
+        <v>122291574</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1586,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498056</v>
+        <v>498338</v>
       </c>
       <c r="R10" t="n">
-        <v>7070237</v>
+        <v>7070474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291576</v>
+        <v>122291567</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1693,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498249</v>
+        <v>498038</v>
       </c>
       <c r="R11" t="n">
-        <v>7070325</v>
+        <v>7070174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291574</v>
+        <v>122291577</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1800,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498338</v>
+        <v>498167</v>
       </c>
       <c r="R12" t="n">
-        <v>7070474</v>
+        <v>7070254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291577</v>
+        <v>122291575</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1907,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498167</v>
+        <v>498330</v>
       </c>
       <c r="R13" t="n">
-        <v>7070254</v>
+        <v>7070466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291568</v>
+        <v>122291584</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2007,17 +1992,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498247</v>
+        <v>497959</v>
       </c>
       <c r="R14" t="n">
-        <v>7070260</v>
+        <v>7070233</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2050,11 +2055,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291567</v>
+        <v>122291579</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498038</v>
+        <v>498060</v>
       </c>
       <c r="R16" t="n">
-        <v>7070174</v>
+        <v>7070326</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291580</v>
+        <v>122291570</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498114</v>
+        <v>498390</v>
       </c>
       <c r="R17" t="n">
-        <v>7070295</v>
+        <v>7070534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291570</v>
+        <v>122291585</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498390</v>
+        <v>497973</v>
       </c>
       <c r="R18" t="n">
-        <v>7070534</v>
+        <v>7070257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291573</v>
+        <v>122291572</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498343</v>
+        <v>498387</v>
       </c>
       <c r="R19" t="n">
-        <v>7070472</v>
+        <v>7070463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291581</v>
+        <v>122291573</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498055</v>
+        <v>498343</v>
       </c>
       <c r="R20" t="n">
-        <v>7070278</v>
+        <v>7070472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291572</v>
+        <v>122291580</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498387</v>
+        <v>498114</v>
       </c>
       <c r="R21" t="n">
-        <v>7070463</v>
+        <v>7070295</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291585</v>
+        <v>122291563</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497973</v>
+        <v>497800</v>
       </c>
       <c r="R22" t="n">
-        <v>7070257</v>
+        <v>7070212</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291564</v>
+        <v>122291569</v>
       </c>
       <c r="B23" t="n">
         <v>57374</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497847</v>
+        <v>498385</v>
       </c>
       <c r="R23" t="n">
-        <v>7070241</v>
+        <v>7070568</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291582</v>
+        <v>122291565</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498057</v>
+        <v>498003</v>
       </c>
       <c r="R24" t="n">
-        <v>7070278</v>
+        <v>7070188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291581</v>
+        <v>122291571</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498055</v>
+        <v>498388</v>
       </c>
       <c r="R2" t="n">
-        <v>7070278</v>
+        <v>7070466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291576</v>
+        <v>122291572</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498249</v>
+        <v>498387</v>
       </c>
       <c r="R3" t="n">
-        <v>7070325</v>
+        <v>7070463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291578</v>
+        <v>122291563</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498060</v>
+        <v>497800</v>
       </c>
       <c r="R4" t="n">
-        <v>7070363</v>
+        <v>7070212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291571</v>
+        <v>122291576</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498388</v>
+        <v>498249</v>
       </c>
       <c r="R5" t="n">
-        <v>7070466</v>
+        <v>7070325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291582</v>
+        <v>122291581</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498057</v>
+        <v>498055</v>
       </c>
       <c r="R6" t="n">
         <v>7070278</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291568</v>
+        <v>122291583</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498247</v>
+        <v>498056</v>
       </c>
       <c r="R7" t="n">
-        <v>7070260</v>
+        <v>7070237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291564</v>
+        <v>122291585</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497847</v>
+        <v>497973</v>
       </c>
       <c r="R8" t="n">
-        <v>7070241</v>
+        <v>7070257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291583</v>
+        <v>122291584</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1457,17 +1457,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498056</v>
+        <v>497959</v>
       </c>
       <c r="R9" t="n">
-        <v>7070237</v>
+        <v>7070233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1520,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291574</v>
+        <v>122291565</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1571,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498338</v>
+        <v>498003</v>
       </c>
       <c r="R10" t="n">
-        <v>7070474</v>
+        <v>7070188</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291567</v>
+        <v>122291573</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1678,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498038</v>
+        <v>498343</v>
       </c>
       <c r="R11" t="n">
-        <v>7070174</v>
+        <v>7070472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291577</v>
+        <v>122291566</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1785,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498167</v>
+        <v>498034</v>
       </c>
       <c r="R12" t="n">
-        <v>7070254</v>
+        <v>7070179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291575</v>
+        <v>122291574</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1892,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498330</v>
+        <v>498338</v>
       </c>
       <c r="R13" t="n">
-        <v>7070466</v>
+        <v>7070474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291584</v>
+        <v>122291582</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -1992,37 +2007,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497959</v>
+        <v>498057</v>
       </c>
       <c r="R14" t="n">
-        <v>7070233</v>
+        <v>7070278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,6 +2050,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291566</v>
+        <v>122291577</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498034</v>
+        <v>498167</v>
       </c>
       <c r="R15" t="n">
-        <v>7070179</v>
+        <v>7070254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291579</v>
+        <v>122291578</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2231,7 +2231,7 @@
         <v>498060</v>
       </c>
       <c r="R16" t="n">
-        <v>7070326</v>
+        <v>7070363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291570</v>
+        <v>122291568</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498390</v>
+        <v>498247</v>
       </c>
       <c r="R17" t="n">
-        <v>7070534</v>
+        <v>7070260</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291585</v>
+        <v>122291575</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497973</v>
+        <v>498330</v>
       </c>
       <c r="R18" t="n">
-        <v>7070257</v>
+        <v>7070466</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291572</v>
+        <v>122291564</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498387</v>
+        <v>497847</v>
       </c>
       <c r="R19" t="n">
-        <v>7070463</v>
+        <v>7070241</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291573</v>
+        <v>122291569</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498343</v>
+        <v>498385</v>
       </c>
       <c r="R20" t="n">
-        <v>7070472</v>
+        <v>7070568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291563</v>
+        <v>122291570</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497800</v>
+        <v>498390</v>
       </c>
       <c r="R22" t="n">
-        <v>7070212</v>
+        <v>7070534</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291569</v>
+        <v>122291567</v>
       </c>
       <c r="B23" t="n">
         <v>57374</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498385</v>
+        <v>498038</v>
       </c>
       <c r="R23" t="n">
-        <v>7070568</v>
+        <v>7070174</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291565</v>
+        <v>122291579</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498003</v>
+        <v>498060</v>
       </c>
       <c r="R24" t="n">
-        <v>7070188</v>
+        <v>7070326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291571</v>
+        <v>122291582</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498388</v>
+        <v>498057</v>
       </c>
       <c r="R2" t="n">
-        <v>7070466</v>
+        <v>7070278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291572</v>
+        <v>122291576</v>
       </c>
       <c r="B3" t="n">
         <v>57374</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498387</v>
+        <v>498249</v>
       </c>
       <c r="R3" t="n">
-        <v>7070463</v>
+        <v>7070325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291563</v>
+        <v>122291566</v>
       </c>
       <c r="B4" t="n">
         <v>57374</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497800</v>
+        <v>498034</v>
       </c>
       <c r="R4" t="n">
-        <v>7070212</v>
+        <v>7070179</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291576</v>
+        <v>122291584</v>
       </c>
       <c r="B5" t="n">
         <v>57374</v>
@@ -1029,17 +1029,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498249</v>
+        <v>497959</v>
       </c>
       <c r="R5" t="n">
-        <v>7070325</v>
+        <v>7070233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291581</v>
+        <v>122291569</v>
       </c>
       <c r="B6" t="n">
         <v>57374</v>
@@ -1143,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498055</v>
+        <v>498385</v>
       </c>
       <c r="R6" t="n">
-        <v>7070278</v>
+        <v>7070568</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291583</v>
+        <v>122291581</v>
       </c>
       <c r="B7" t="n">
         <v>57374</v>
@@ -1250,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498056</v>
+        <v>498055</v>
       </c>
       <c r="R7" t="n">
-        <v>7070237</v>
+        <v>7070278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291585</v>
+        <v>122291571</v>
       </c>
       <c r="B8" t="n">
         <v>57374</v>
@@ -1357,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497973</v>
+        <v>498388</v>
       </c>
       <c r="R8" t="n">
-        <v>7070257</v>
+        <v>7070466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1412,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291584</v>
+        <v>122291573</v>
       </c>
       <c r="B9" t="n">
         <v>57374</v>
@@ -1457,37 +1472,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497959</v>
+        <v>498343</v>
       </c>
       <c r="R9" t="n">
-        <v>7070233</v>
+        <v>7070472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291565</v>
+        <v>122291579</v>
       </c>
       <c r="B10" t="n">
         <v>57374</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498003</v>
+        <v>498060</v>
       </c>
       <c r="R10" t="n">
-        <v>7070188</v>
+        <v>7070326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291573</v>
+        <v>122291575</v>
       </c>
       <c r="B11" t="n">
         <v>57374</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498343</v>
+        <v>498330</v>
       </c>
       <c r="R11" t="n">
-        <v>7070472</v>
+        <v>7070466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291566</v>
+        <v>122291583</v>
       </c>
       <c r="B12" t="n">
         <v>57374</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498034</v>
+        <v>498056</v>
       </c>
       <c r="R12" t="n">
-        <v>7070179</v>
+        <v>7070237</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291574</v>
+        <v>122291585</v>
       </c>
       <c r="B13" t="n">
         <v>57374</v>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498338</v>
+        <v>497973</v>
       </c>
       <c r="R13" t="n">
-        <v>7070474</v>
+        <v>7070257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291582</v>
+        <v>122291568</v>
       </c>
       <c r="B14" t="n">
         <v>57374</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498057</v>
+        <v>498247</v>
       </c>
       <c r="R14" t="n">
-        <v>7070278</v>
+        <v>7070260</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291577</v>
+        <v>122291565</v>
       </c>
       <c r="B15" t="n">
         <v>57374</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498167</v>
+        <v>498003</v>
       </c>
       <c r="R15" t="n">
-        <v>7070254</v>
+        <v>7070188</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291578</v>
+        <v>122291567</v>
       </c>
       <c r="B16" t="n">
         <v>57374</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498060</v>
+        <v>498038</v>
       </c>
       <c r="R16" t="n">
-        <v>7070363</v>
+        <v>7070174</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291568</v>
+        <v>122291564</v>
       </c>
       <c r="B17" t="n">
         <v>57374</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498247</v>
+        <v>497847</v>
       </c>
       <c r="R17" t="n">
-        <v>7070260</v>
+        <v>7070241</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291575</v>
+        <v>122291572</v>
       </c>
       <c r="B18" t="n">
         <v>57374</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498330</v>
+        <v>498387</v>
       </c>
       <c r="R18" t="n">
-        <v>7070466</v>
+        <v>7070463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291564</v>
+        <v>122291574</v>
       </c>
       <c r="B19" t="n">
         <v>57374</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497847</v>
+        <v>498338</v>
       </c>
       <c r="R19" t="n">
-        <v>7070241</v>
+        <v>7070474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291569</v>
+        <v>122291570</v>
       </c>
       <c r="B20" t="n">
         <v>57374</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498385</v>
+        <v>498390</v>
       </c>
       <c r="R20" t="n">
-        <v>7070568</v>
+        <v>7070534</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291580</v>
+        <v>122291563</v>
       </c>
       <c r="B21" t="n">
         <v>57374</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498114</v>
+        <v>497800</v>
       </c>
       <c r="R21" t="n">
-        <v>7070295</v>
+        <v>7070212</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291570</v>
+        <v>122291577</v>
       </c>
       <c r="B22" t="n">
         <v>57374</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498390</v>
+        <v>498167</v>
       </c>
       <c r="R22" t="n">
-        <v>7070534</v>
+        <v>7070254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291567</v>
+        <v>122291578</v>
       </c>
       <c r="B23" t="n">
         <v>57374</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498038</v>
+        <v>498060</v>
       </c>
       <c r="R23" t="n">
-        <v>7070174</v>
+        <v>7070363</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291579</v>
+        <v>122291580</v>
       </c>
       <c r="B24" t="n">
         <v>57374</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498060</v>
+        <v>498114</v>
       </c>
       <c r="R24" t="n">
-        <v>7070326</v>
+        <v>7070295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291582</v>
+        <v>122291566</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498057</v>
+        <v>498034</v>
       </c>
       <c r="R2" t="n">
-        <v>7070278</v>
+        <v>7070179</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>122291576</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291566</v>
+        <v>122291567</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498034</v>
+        <v>498038</v>
       </c>
       <c r="R4" t="n">
-        <v>7070179</v>
+        <v>7070174</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291584</v>
+        <v>122291583</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,37 +1029,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497959</v>
+        <v>498056</v>
       </c>
       <c r="R5" t="n">
-        <v>7070233</v>
+        <v>7070237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291569</v>
+        <v>122291580</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498385</v>
+        <v>498114</v>
       </c>
       <c r="R6" t="n">
-        <v>7070568</v>
+        <v>7070295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291581</v>
+        <v>122291577</v>
       </c>
       <c r="B7" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498055</v>
+        <v>498167</v>
       </c>
       <c r="R7" t="n">
-        <v>7070278</v>
+        <v>7070254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291571</v>
+        <v>122291584</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,17 +1350,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498388</v>
+        <v>497959</v>
       </c>
       <c r="R8" t="n">
-        <v>7070466</v>
+        <v>7070233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,11 +1413,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291573</v>
+        <v>122291570</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498343</v>
+        <v>498390</v>
       </c>
       <c r="R9" t="n">
-        <v>7070472</v>
+        <v>7070534</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291579</v>
+        <v>122291582</v>
       </c>
       <c r="B10" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498060</v>
+        <v>498057</v>
       </c>
       <c r="R10" t="n">
-        <v>7070326</v>
+        <v>7070278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291575</v>
+        <v>122291581</v>
       </c>
       <c r="B11" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498330</v>
+        <v>498055</v>
       </c>
       <c r="R11" t="n">
-        <v>7070466</v>
+        <v>7070278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291583</v>
+        <v>122291573</v>
       </c>
       <c r="B12" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498056</v>
+        <v>498343</v>
       </c>
       <c r="R12" t="n">
-        <v>7070237</v>
+        <v>7070472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291585</v>
+        <v>122291571</v>
       </c>
       <c r="B13" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497973</v>
+        <v>498388</v>
       </c>
       <c r="R13" t="n">
-        <v>7070257</v>
+        <v>7070466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291568</v>
+        <v>122291572</v>
       </c>
       <c r="B14" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498247</v>
+        <v>498387</v>
       </c>
       <c r="R14" t="n">
-        <v>7070260</v>
+        <v>7070463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291565</v>
+        <v>122291563</v>
       </c>
       <c r="B15" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498003</v>
+        <v>497800</v>
       </c>
       <c r="R15" t="n">
-        <v>7070188</v>
+        <v>7070212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291567</v>
+        <v>122291569</v>
       </c>
       <c r="B16" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498038</v>
+        <v>498385</v>
       </c>
       <c r="R16" t="n">
-        <v>7070174</v>
+        <v>7070568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291564</v>
+        <v>122291585</v>
       </c>
       <c r="B17" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497847</v>
+        <v>497973</v>
       </c>
       <c r="R17" t="n">
-        <v>7070241</v>
+        <v>7070257</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291572</v>
+        <v>122291575</v>
       </c>
       <c r="B18" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498387</v>
+        <v>498330</v>
       </c>
       <c r="R18" t="n">
-        <v>7070463</v>
+        <v>7070466</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291574</v>
+        <v>122291565</v>
       </c>
       <c r="B19" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498338</v>
+        <v>498003</v>
       </c>
       <c r="R19" t="n">
-        <v>7070474</v>
+        <v>7070188</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291570</v>
+        <v>122291564</v>
       </c>
       <c r="B20" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498390</v>
+        <v>497847</v>
       </c>
       <c r="R20" t="n">
-        <v>7070534</v>
+        <v>7070241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291563</v>
+        <v>122291568</v>
       </c>
       <c r="B21" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497800</v>
+        <v>498247</v>
       </c>
       <c r="R21" t="n">
-        <v>7070212</v>
+        <v>7070260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291577</v>
+        <v>122291578</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498167</v>
+        <v>498060</v>
       </c>
       <c r="R22" t="n">
-        <v>7070254</v>
+        <v>7070363</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291578</v>
+        <v>122291579</v>
       </c>
       <c r="B23" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>498060</v>
       </c>
       <c r="R23" t="n">
-        <v>7070363</v>
+        <v>7070326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291580</v>
+        <v>122291574</v>
       </c>
       <c r="B24" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498114</v>
+        <v>498338</v>
       </c>
       <c r="R24" t="n">
-        <v>7070295</v>
+        <v>7070474</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291566</v>
+        <v>122291577</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498034</v>
+        <v>498167</v>
       </c>
       <c r="R2" t="n">
-        <v>7070179</v>
+        <v>7070254</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291576</v>
+        <v>122291570</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498249</v>
+        <v>498390</v>
       </c>
       <c r="R3" t="n">
-        <v>7070325</v>
+        <v>7070534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291567</v>
+        <v>122291564</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498038</v>
+        <v>497847</v>
       </c>
       <c r="R4" t="n">
-        <v>7070174</v>
+        <v>7070241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291583</v>
+        <v>122291584</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1029,17 +1029,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498056</v>
+        <v>497959</v>
       </c>
       <c r="R5" t="n">
-        <v>7070237</v>
+        <v>7070233</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291580</v>
+        <v>122291578</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1143,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498114</v>
+        <v>498060</v>
       </c>
       <c r="R6" t="n">
-        <v>7070295</v>
+        <v>7070363</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291577</v>
+        <v>122291572</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1250,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498167</v>
+        <v>498387</v>
       </c>
       <c r="R7" t="n">
-        <v>7070254</v>
+        <v>7070463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291584</v>
+        <v>122291579</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1350,37 +1365,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497959</v>
+        <v>498060</v>
       </c>
       <c r="R8" t="n">
-        <v>7070233</v>
+        <v>7070326</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291570</v>
+        <v>122291582</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498390</v>
+        <v>498057</v>
       </c>
       <c r="R9" t="n">
-        <v>7070534</v>
+        <v>7070278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291582</v>
+        <v>122291583</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498057</v>
+        <v>498056</v>
       </c>
       <c r="R10" t="n">
-        <v>7070278</v>
+        <v>7070237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291581</v>
+        <v>122291575</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498055</v>
+        <v>498330</v>
       </c>
       <c r="R11" t="n">
-        <v>7070278</v>
+        <v>7070466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291573</v>
+        <v>122291571</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498343</v>
+        <v>498388</v>
       </c>
       <c r="R12" t="n">
-        <v>7070472</v>
+        <v>7070466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291571</v>
+        <v>122291580</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498388</v>
+        <v>498114</v>
       </c>
       <c r="R13" t="n">
-        <v>7070466</v>
+        <v>7070295</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291572</v>
+        <v>122291581</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498387</v>
+        <v>498055</v>
       </c>
       <c r="R14" t="n">
-        <v>7070463</v>
+        <v>7070278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291563</v>
+        <v>122291574</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497800</v>
+        <v>498338</v>
       </c>
       <c r="R15" t="n">
-        <v>7070212</v>
+        <v>7070474</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291569</v>
+        <v>122291568</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498385</v>
+        <v>498247</v>
       </c>
       <c r="R16" t="n">
-        <v>7070568</v>
+        <v>7070260</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291585</v>
+        <v>122291569</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497973</v>
+        <v>498385</v>
       </c>
       <c r="R17" t="n">
-        <v>7070257</v>
+        <v>7070568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291575</v>
+        <v>122291585</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498330</v>
+        <v>497973</v>
       </c>
       <c r="R18" t="n">
-        <v>7070466</v>
+        <v>7070257</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291565</v>
+        <v>122291567</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498003</v>
+        <v>498038</v>
       </c>
       <c r="R19" t="n">
-        <v>7070188</v>
+        <v>7070174</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291564</v>
+        <v>122291565</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497847</v>
+        <v>498003</v>
       </c>
       <c r="R20" t="n">
-        <v>7070241</v>
+        <v>7070188</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291568</v>
+        <v>122291573</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498247</v>
+        <v>498343</v>
       </c>
       <c r="R21" t="n">
-        <v>7070260</v>
+        <v>7070472</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291578</v>
+        <v>122291576</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498060</v>
+        <v>498249</v>
       </c>
       <c r="R22" t="n">
-        <v>7070363</v>
+        <v>7070325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291579</v>
+        <v>122291566</v>
       </c>
       <c r="B23" t="n">
         <v>57379</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498060</v>
+        <v>498034</v>
       </c>
       <c r="R23" t="n">
-        <v>7070326</v>
+        <v>7070179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291574</v>
+        <v>122291563</v>
       </c>
       <c r="B24" t="n">
         <v>57379</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498338</v>
+        <v>497800</v>
       </c>
       <c r="R24" t="n">
-        <v>7070474</v>
+        <v>7070212</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291581</v>
+        <v>122291574</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498055</v>
+        <v>498338</v>
       </c>
       <c r="R14" t="n">
-        <v>7070278</v>
+        <v>7070474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291574</v>
+        <v>122291568</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498338</v>
+        <v>498247</v>
       </c>
       <c r="R15" t="n">
-        <v>7070474</v>
+        <v>7070260</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291568</v>
+        <v>122291569</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498247</v>
+        <v>498385</v>
       </c>
       <c r="R16" t="n">
-        <v>7070260</v>
+        <v>7070568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291569</v>
+        <v>122291581</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498385</v>
+        <v>498055</v>
       </c>
       <c r="R17" t="n">
-        <v>7070568</v>
+        <v>7070278</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291570</v>
+        <v>122291579</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -800,11 +795,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498390</v>
+        <v>498060</v>
       </c>
       <c r="R3" t="n">
-        <v>7070534</v>
+        <v>7070326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291564</v>
+        <v>122291570</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -907,11 +897,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497847</v>
+        <v>498390</v>
       </c>
       <c r="R4" t="n">
-        <v>7070241</v>
+        <v>7070534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291584</v>
+        <v>122291580</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1014,11 +999,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1029,37 +1009,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497959</v>
+        <v>498114</v>
       </c>
       <c r="R5" t="n">
-        <v>7070233</v>
+        <v>7070295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291578</v>
+        <v>122291576</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1136,11 +1101,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1158,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498060</v>
+        <v>498249</v>
       </c>
       <c r="R6" t="n">
-        <v>7070363</v>
+        <v>7070325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291572</v>
+        <v>122291583</v>
       </c>
       <c r="B7" t="n">
         <v>57379</v>
@@ -1243,11 +1203,6 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1265,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498387</v>
+        <v>498056</v>
       </c>
       <c r="R7" t="n">
-        <v>7070463</v>
+        <v>7070237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291579</v>
+        <v>122291565</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1350,11 +1305,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1372,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498060</v>
+        <v>498003</v>
       </c>
       <c r="R8" t="n">
-        <v>7070326</v>
+        <v>7070188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291582</v>
+        <v>122291572</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1457,11 +1407,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1479,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498057</v>
+        <v>498387</v>
       </c>
       <c r="R9" t="n">
-        <v>7070278</v>
+        <v>7070463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1464,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291583</v>
+        <v>122291571</v>
       </c>
       <c r="B10" t="n">
         <v>57379</v>
@@ -1564,11 +1509,6 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1586,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498056</v>
+        <v>498388</v>
       </c>
       <c r="R10" t="n">
-        <v>7070237</v>
+        <v>7070466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291575</v>
+        <v>122291582</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1671,11 +1611,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1693,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498330</v>
+        <v>498057</v>
       </c>
       <c r="R11" t="n">
-        <v>7070466</v>
+        <v>7070278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291571</v>
+        <v>122291584</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1778,11 +1713,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1793,17 +1723,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498388</v>
+        <v>497959</v>
       </c>
       <c r="R12" t="n">
-        <v>7070466</v>
+        <v>7070233</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291580</v>
+        <v>122291568</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1885,11 +1830,6 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1907,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498114</v>
+        <v>498247</v>
       </c>
       <c r="R13" t="n">
-        <v>7070295</v>
+        <v>7070260</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291574</v>
+        <v>122291563</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -1992,11 +1932,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2014,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498338</v>
+        <v>497800</v>
       </c>
       <c r="R14" t="n">
-        <v>7070474</v>
+        <v>7070212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291568</v>
+        <v>122291566</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2099,11 +2034,6 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2121,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498247</v>
+        <v>498034</v>
       </c>
       <c r="R15" t="n">
-        <v>7070260</v>
+        <v>7070179</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2091,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,7 +2118,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291569</v>
+        <v>122291581</v>
       </c>
       <c r="B16" t="n">
         <v>57379</v>
@@ -2206,11 +2136,6 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2228,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498385</v>
+        <v>498055</v>
       </c>
       <c r="R16" t="n">
-        <v>7070568</v>
+        <v>7070278</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2193,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291581</v>
+        <v>122291578</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2313,11 +2238,6 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2335,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498055</v>
+        <v>498060</v>
       </c>
       <c r="R17" t="n">
-        <v>7070278</v>
+        <v>7070363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291585</v>
+        <v>122291567</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2420,11 +2340,6 @@
       <c r="E18" t="n">
         <v>100109</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2442,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497973</v>
+        <v>498038</v>
       </c>
       <c r="R18" t="n">
-        <v>7070257</v>
+        <v>7070174</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2397,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291567</v>
+        <v>122291569</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2527,11 +2442,6 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2549,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498038</v>
+        <v>498385</v>
       </c>
       <c r="R19" t="n">
-        <v>7070174</v>
+        <v>7070568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2499,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291565</v>
+        <v>122291573</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2634,11 +2544,6 @@
       <c r="E20" t="n">
         <v>100109</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2656,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498003</v>
+        <v>498343</v>
       </c>
       <c r="R20" t="n">
-        <v>7070188</v>
+        <v>7070472</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2628,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291573</v>
+        <v>122291575</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2741,11 +2646,6 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2763,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498343</v>
+        <v>498330</v>
       </c>
       <c r="R21" t="n">
-        <v>7070472</v>
+        <v>7070466</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2703,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291576</v>
+        <v>122291574</v>
       </c>
       <c r="B22" t="n">
         <v>57379</v>
@@ -2848,11 +2748,6 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2870,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498249</v>
+        <v>498338</v>
       </c>
       <c r="R22" t="n">
-        <v>7070325</v>
+        <v>7070474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2832,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291566</v>
+        <v>122291564</v>
       </c>
       <c r="B23" t="n">
         <v>57379</v>
@@ -2955,11 +2850,6 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2977,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498034</v>
+        <v>497847</v>
       </c>
       <c r="R23" t="n">
-        <v>7070179</v>
+        <v>7070241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +2907,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291563</v>
+        <v>122291585</v>
       </c>
       <c r="B24" t="n">
         <v>57379</v>
@@ -3062,11 +2952,6 @@
       <c r="E24" t="n">
         <v>100109</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3084,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497800</v>
+        <v>497973</v>
       </c>
       <c r="R24" t="n">
-        <v>7070212</v>
+        <v>7070257</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3009,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -2322,7 +2322,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291567</v>
+        <v>122291569</v>
       </c>
       <c r="B18" t="n">
         <v>57379</v>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498038</v>
+        <v>498385</v>
       </c>
       <c r="R18" t="n">
-        <v>7070174</v>
+        <v>7070568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,7 +2424,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291569</v>
+        <v>122291567</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498385</v>
+        <v>498038</v>
       </c>
       <c r="R19" t="n">
-        <v>7070568</v>
+        <v>7070174</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291577</v>
+        <v>122291565</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498167</v>
+        <v>498003</v>
       </c>
       <c r="R2" t="n">
-        <v>7070254</v>
+        <v>7070188</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291579</v>
+        <v>122291571</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,6 +800,11 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -812,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498060</v>
+        <v>498388</v>
       </c>
       <c r="R3" t="n">
-        <v>7070326</v>
+        <v>7070466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291570</v>
+        <v>122291564</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,6 +907,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -914,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498390</v>
+        <v>497847</v>
       </c>
       <c r="R4" t="n">
-        <v>7070534</v>
+        <v>7070241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291580</v>
+        <v>122291574</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,6 +1014,11 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1016,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498114</v>
+        <v>498338</v>
       </c>
       <c r="R5" t="n">
-        <v>7070295</v>
+        <v>7070474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291576</v>
+        <v>122291579</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,6 +1121,11 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1118,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498249</v>
+        <v>498060</v>
       </c>
       <c r="R6" t="n">
-        <v>7070325</v>
+        <v>7070326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291583</v>
+        <v>122291580</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,6 +1228,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1220,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498056</v>
+        <v>498114</v>
       </c>
       <c r="R7" t="n">
-        <v>7070237</v>
+        <v>7070295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291565</v>
+        <v>122291567</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,6 +1335,11 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1322,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498003</v>
+        <v>498038</v>
       </c>
       <c r="R8" t="n">
-        <v>7070188</v>
+        <v>7070174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291572</v>
+        <v>122291566</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1407,6 +1442,11 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1424,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498387</v>
+        <v>498034</v>
       </c>
       <c r="R9" t="n">
-        <v>7070463</v>
+        <v>7070179</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291571</v>
+        <v>122291581</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1509,6 +1549,11 @@
       <c r="E10" t="n">
         <v>100109</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1526,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498388</v>
+        <v>498055</v>
       </c>
       <c r="R10" t="n">
-        <v>7070466</v>
+        <v>7070278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291582</v>
+        <v>122291578</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1611,6 +1656,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1628,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498057</v>
+        <v>498060</v>
       </c>
       <c r="R11" t="n">
-        <v>7070278</v>
+        <v>7070363</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291584</v>
+        <v>122291577</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1713,6 +1763,11 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1723,37 +1778,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497959</v>
+        <v>498167</v>
       </c>
       <c r="R12" t="n">
-        <v>7070233</v>
+        <v>7070254</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291568</v>
+        <v>122291575</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,6 +1870,11 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1847,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498247</v>
+        <v>498330</v>
       </c>
       <c r="R13" t="n">
-        <v>7070260</v>
+        <v>7070466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291563</v>
+        <v>122291582</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,6 +1977,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1949,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497800</v>
+        <v>498057</v>
       </c>
       <c r="R14" t="n">
-        <v>7070212</v>
+        <v>7070278</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291566</v>
+        <v>122291585</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2034,6 +2084,11 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2051,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498034</v>
+        <v>497973</v>
       </c>
       <c r="R15" t="n">
-        <v>7070179</v>
+        <v>7070257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291581</v>
+        <v>122291569</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,6 +2191,11 @@
       <c r="E16" t="n">
         <v>100109</v>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2153,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498055</v>
+        <v>498385</v>
       </c>
       <c r="R16" t="n">
-        <v>7070278</v>
+        <v>7070568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2220,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291578</v>
+        <v>122291572</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2238,6 +2298,11 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2255,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498060</v>
+        <v>498387</v>
       </c>
       <c r="R17" t="n">
-        <v>7070363</v>
+        <v>7070463</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291569</v>
+        <v>122291576</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,6 +2405,11 @@
       <c r="E18" t="n">
         <v>100109</v>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2357,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498385</v>
+        <v>498249</v>
       </c>
       <c r="R18" t="n">
-        <v>7070568</v>
+        <v>7070325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2424,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291567</v>
+        <v>122291568</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,6 +2512,11 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2459,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498038</v>
+        <v>498247</v>
       </c>
       <c r="R19" t="n">
-        <v>7070174</v>
+        <v>7070260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291573</v>
+        <v>122291563</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2544,6 +2619,11 @@
       <c r="E20" t="n">
         <v>100109</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2561,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498343</v>
+        <v>497800</v>
       </c>
       <c r="R20" t="n">
-        <v>7070472</v>
+        <v>7070212</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291575</v>
+        <v>122291573</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2646,6 +2726,11 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2663,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498330</v>
+        <v>498343</v>
       </c>
       <c r="R21" t="n">
-        <v>7070466</v>
+        <v>7070472</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,7 +2788,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2730,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291574</v>
+        <v>122291583</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2748,6 +2833,11 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2765,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498338</v>
+        <v>498056</v>
       </c>
       <c r="R22" t="n">
-        <v>7070474</v>
+        <v>7070237</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2805,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2832,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291564</v>
+        <v>122291584</v>
       </c>
       <c r="B23" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2850,6 +2940,11 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2860,17 +2955,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497847</v>
+        <v>497959</v>
       </c>
       <c r="R23" t="n">
-        <v>7070241</v>
+        <v>7070233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,11 +3018,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291585</v>
+        <v>122291570</v>
       </c>
       <c r="B24" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2952,6 +3062,11 @@
       <c r="E24" t="n">
         <v>100109</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2969,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497973</v>
+        <v>498390</v>
       </c>
       <c r="R24" t="n">
-        <v>7070257</v>
+        <v>7070534</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291565</v>
+        <v>122291569</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498003</v>
+        <v>498385</v>
       </c>
       <c r="R2" t="n">
-        <v>7070188</v>
+        <v>7070568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291571</v>
+        <v>122291573</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498388</v>
+        <v>498343</v>
       </c>
       <c r="R3" t="n">
-        <v>7070466</v>
+        <v>7070472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291564</v>
+        <v>122291577</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497847</v>
+        <v>498167</v>
       </c>
       <c r="R4" t="n">
-        <v>7070241</v>
+        <v>7070254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291574</v>
+        <v>122291564</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498338</v>
+        <v>497847</v>
       </c>
       <c r="R5" t="n">
-        <v>7070474</v>
+        <v>7070241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291580</v>
+        <v>122291584</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1243,17 +1243,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498114</v>
+        <v>497959</v>
       </c>
       <c r="R7" t="n">
-        <v>7070295</v>
+        <v>7070233</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1306,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291567</v>
+        <v>122291585</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1357,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498038</v>
+        <v>497973</v>
       </c>
       <c r="R8" t="n">
-        <v>7070174</v>
+        <v>7070257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1412,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291566</v>
+        <v>122291576</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1464,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498034</v>
+        <v>498249</v>
       </c>
       <c r="R9" t="n">
-        <v>7070179</v>
+        <v>7070325</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1519,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291581</v>
+        <v>122291583</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1571,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498055</v>
+        <v>498056</v>
       </c>
       <c r="R10" t="n">
-        <v>7070278</v>
+        <v>7070237</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291578</v>
+        <v>122291563</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1678,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498060</v>
+        <v>497800</v>
       </c>
       <c r="R11" t="n">
-        <v>7070363</v>
+        <v>7070212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291577</v>
+        <v>122291571</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1785,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498167</v>
+        <v>498388</v>
       </c>
       <c r="R12" t="n">
-        <v>7070254</v>
+        <v>7070466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291575</v>
+        <v>122291568</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1892,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498330</v>
+        <v>498247</v>
       </c>
       <c r="R13" t="n">
-        <v>7070466</v>
+        <v>7070260</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291582</v>
+        <v>122291574</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -1999,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498057</v>
+        <v>498338</v>
       </c>
       <c r="R14" t="n">
-        <v>7070278</v>
+        <v>7070474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291585</v>
+        <v>122291572</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2106,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497973</v>
+        <v>498387</v>
       </c>
       <c r="R15" t="n">
-        <v>7070257</v>
+        <v>7070463</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2161,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291569</v>
+        <v>122291575</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2213,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498385</v>
+        <v>498330</v>
       </c>
       <c r="R16" t="n">
-        <v>7070568</v>
+        <v>7070466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291572</v>
+        <v>122291565</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498387</v>
+        <v>498003</v>
       </c>
       <c r="R17" t="n">
-        <v>7070463</v>
+        <v>7070188</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291576</v>
+        <v>122291582</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2427,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498249</v>
+        <v>498057</v>
       </c>
       <c r="R18" t="n">
-        <v>7070325</v>
+        <v>7070278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291568</v>
+        <v>122291570</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2534,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498247</v>
+        <v>498390</v>
       </c>
       <c r="R19" t="n">
-        <v>7070260</v>
+        <v>7070534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291563</v>
+        <v>122291578</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2641,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497800</v>
+        <v>498060</v>
       </c>
       <c r="R20" t="n">
-        <v>7070212</v>
+        <v>7070363</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291573</v>
+        <v>122291567</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2748,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498343</v>
+        <v>498038</v>
       </c>
       <c r="R21" t="n">
-        <v>7070472</v>
+        <v>7070174</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291583</v>
+        <v>122291581</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2855,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498056</v>
+        <v>498055</v>
       </c>
       <c r="R22" t="n">
-        <v>7070237</v>
+        <v>7070278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291584</v>
+        <v>122291566</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -2955,37 +2970,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497959</v>
+        <v>498034</v>
       </c>
       <c r="R23" t="n">
-        <v>7070233</v>
+        <v>7070179</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,6 +3013,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291570</v>
+        <v>122291580</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498390</v>
+        <v>498114</v>
       </c>
       <c r="R24" t="n">
-        <v>7070534</v>
+        <v>7070295</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291583</v>
+        <v>122291571</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498056</v>
+        <v>498388</v>
       </c>
       <c r="R10" t="n">
-        <v>7070237</v>
+        <v>7070466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291563</v>
+        <v>122291583</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497800</v>
+        <v>498056</v>
       </c>
       <c r="R11" t="n">
-        <v>7070212</v>
+        <v>7070237</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291571</v>
+        <v>122291563</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498388</v>
+        <v>497800</v>
       </c>
       <c r="R12" t="n">
-        <v>7070466</v>
+        <v>7070212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291569</v>
+        <v>122291578</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498385</v>
+        <v>498060</v>
       </c>
       <c r="R2" t="n">
-        <v>7070568</v>
+        <v>7070363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291573</v>
+        <v>122291565</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498343</v>
+        <v>498003</v>
       </c>
       <c r="R3" t="n">
-        <v>7070472</v>
+        <v>7070188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291577</v>
+        <v>122291573</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498167</v>
+        <v>498343</v>
       </c>
       <c r="R4" t="n">
-        <v>7070254</v>
+        <v>7070472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291564</v>
+        <v>122291575</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497847</v>
+        <v>498330</v>
       </c>
       <c r="R5" t="n">
-        <v>7070241</v>
+        <v>7070466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291579</v>
+        <v>122291577</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498060</v>
+        <v>498167</v>
       </c>
       <c r="R6" t="n">
-        <v>7070326</v>
+        <v>7070254</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291585</v>
+        <v>122291574</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497973</v>
+        <v>498338</v>
       </c>
       <c r="R8" t="n">
-        <v>7070257</v>
+        <v>7070474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291576</v>
+        <v>122291580</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498249</v>
+        <v>498114</v>
       </c>
       <c r="R9" t="n">
-        <v>7070325</v>
+        <v>7070295</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291571</v>
+        <v>122291563</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498388</v>
+        <v>497800</v>
       </c>
       <c r="R10" t="n">
-        <v>7070466</v>
+        <v>7070212</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291583</v>
+        <v>122291572</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498056</v>
+        <v>498387</v>
       </c>
       <c r="R11" t="n">
-        <v>7070237</v>
+        <v>7070463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291563</v>
+        <v>122291582</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497800</v>
+        <v>498057</v>
       </c>
       <c r="R12" t="n">
-        <v>7070212</v>
+        <v>7070278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291568</v>
+        <v>122291569</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498247</v>
+        <v>498385</v>
       </c>
       <c r="R13" t="n">
-        <v>7070260</v>
+        <v>7070568</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291574</v>
+        <v>122291567</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498338</v>
+        <v>498038</v>
       </c>
       <c r="R14" t="n">
-        <v>7070474</v>
+        <v>7070174</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291572</v>
+        <v>122291570</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498387</v>
+        <v>498390</v>
       </c>
       <c r="R15" t="n">
-        <v>7070463</v>
+        <v>7070534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291575</v>
+        <v>122291571</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498330</v>
+        <v>498388</v>
       </c>
       <c r="R16" t="n">
         <v>7070466</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291565</v>
+        <v>122291576</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498003</v>
+        <v>498249</v>
       </c>
       <c r="R17" t="n">
-        <v>7070188</v>
+        <v>7070325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291582</v>
+        <v>122291566</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498057</v>
+        <v>498034</v>
       </c>
       <c r="R18" t="n">
-        <v>7070278</v>
+        <v>7070179</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291570</v>
+        <v>122291581</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498390</v>
+        <v>498055</v>
       </c>
       <c r="R19" t="n">
-        <v>7070534</v>
+        <v>7070278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291578</v>
+        <v>122291564</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498060</v>
+        <v>497847</v>
       </c>
       <c r="R20" t="n">
-        <v>7070363</v>
+        <v>7070241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291567</v>
+        <v>122291568</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498038</v>
+        <v>498247</v>
       </c>
       <c r="R21" t="n">
-        <v>7070174</v>
+        <v>7070260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291581</v>
+        <v>122291579</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498055</v>
+        <v>498060</v>
       </c>
       <c r="R22" t="n">
-        <v>7070278</v>
+        <v>7070326</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291566</v>
+        <v>122291585</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498034</v>
+        <v>497973</v>
       </c>
       <c r="R23" t="n">
-        <v>7070179</v>
+        <v>7070257</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291580</v>
+        <v>122291583</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498114</v>
+        <v>498056</v>
       </c>
       <c r="R24" t="n">
-        <v>7070295</v>
+        <v>7070237</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291578</v>
+        <v>122291577</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498060</v>
+        <v>498167</v>
       </c>
       <c r="R2" t="n">
-        <v>7070363</v>
+        <v>7070254</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291565</v>
+        <v>122291564</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498003</v>
+        <v>497847</v>
       </c>
       <c r="R3" t="n">
-        <v>7070188</v>
+        <v>7070241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291573</v>
+        <v>122291569</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498343</v>
+        <v>498385</v>
       </c>
       <c r="R4" t="n">
-        <v>7070472</v>
+        <v>7070568</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291575</v>
+        <v>122291567</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498330</v>
+        <v>498038</v>
       </c>
       <c r="R5" t="n">
-        <v>7070466</v>
+        <v>7070174</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291577</v>
+        <v>122291570</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498167</v>
+        <v>498390</v>
       </c>
       <c r="R6" t="n">
-        <v>7070254</v>
+        <v>7070534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291584</v>
+        <v>122291566</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1243,37 +1243,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497959</v>
+        <v>498034</v>
       </c>
       <c r="R7" t="n">
-        <v>7070233</v>
+        <v>7070179</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291574</v>
+        <v>122291573</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1372,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498338</v>
+        <v>498343</v>
       </c>
       <c r="R8" t="n">
-        <v>7070474</v>
+        <v>7070472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291580</v>
+        <v>122291581</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1479,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498114</v>
+        <v>498055</v>
       </c>
       <c r="R9" t="n">
-        <v>7070295</v>
+        <v>7070278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291563</v>
+        <v>122291582</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1586,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497800</v>
+        <v>498057</v>
       </c>
       <c r="R10" t="n">
-        <v>7070212</v>
+        <v>7070278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291572</v>
+        <v>122291565</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1693,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498387</v>
+        <v>498003</v>
       </c>
       <c r="R11" t="n">
-        <v>7070463</v>
+        <v>7070188</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291582</v>
+        <v>122291571</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1800,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498057</v>
+        <v>498388</v>
       </c>
       <c r="R12" t="n">
-        <v>7070278</v>
+        <v>7070466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291569</v>
+        <v>122291576</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1907,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498385</v>
+        <v>498249</v>
       </c>
       <c r="R13" t="n">
-        <v>7070568</v>
+        <v>7070325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291567</v>
+        <v>122291572</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -2014,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498038</v>
+        <v>498387</v>
       </c>
       <c r="R14" t="n">
-        <v>7070174</v>
+        <v>7070463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291570</v>
+        <v>122291563</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2121,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498390</v>
+        <v>497800</v>
       </c>
       <c r="R15" t="n">
-        <v>7070534</v>
+        <v>7070212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291571</v>
+        <v>122291583</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2228,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498388</v>
+        <v>498056</v>
       </c>
       <c r="R16" t="n">
-        <v>7070466</v>
+        <v>7070237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291576</v>
+        <v>122291580</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2335,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498249</v>
+        <v>498114</v>
       </c>
       <c r="R17" t="n">
-        <v>7070325</v>
+        <v>7070295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291566</v>
+        <v>122291575</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2442,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498034</v>
+        <v>498330</v>
       </c>
       <c r="R18" t="n">
-        <v>7070179</v>
+        <v>7070466</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291581</v>
+        <v>122291578</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2549,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498055</v>
+        <v>498060</v>
       </c>
       <c r="R19" t="n">
-        <v>7070278</v>
+        <v>7070363</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291564</v>
+        <v>122291584</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2649,17 +2634,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497847</v>
+        <v>497959</v>
       </c>
       <c r="R20" t="n">
-        <v>7070241</v>
+        <v>7070233</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2692,11 +2697,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291568</v>
+        <v>122291579</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498247</v>
+        <v>498060</v>
       </c>
       <c r="R21" t="n">
-        <v>7070260</v>
+        <v>7070326</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291579</v>
+        <v>122291574</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498060</v>
+        <v>498338</v>
       </c>
       <c r="R22" t="n">
-        <v>7070326</v>
+        <v>7070474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291583</v>
+        <v>122291568</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498056</v>
+        <v>498247</v>
       </c>
       <c r="R24" t="n">
-        <v>7070237</v>
+        <v>7070260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291577</v>
+        <v>122291571</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498167</v>
+        <v>498388</v>
       </c>
       <c r="R2" t="n">
-        <v>7070254</v>
+        <v>7070466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291564</v>
+        <v>122291573</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497847</v>
+        <v>498343</v>
       </c>
       <c r="R3" t="n">
-        <v>7070241</v>
+        <v>7070472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291569</v>
+        <v>122291579</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498385</v>
+        <v>498060</v>
       </c>
       <c r="R4" t="n">
-        <v>7070568</v>
+        <v>7070326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291567</v>
+        <v>122291569</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498038</v>
+        <v>498385</v>
       </c>
       <c r="R5" t="n">
-        <v>7070174</v>
+        <v>7070568</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291570</v>
+        <v>122291565</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498390</v>
+        <v>498003</v>
       </c>
       <c r="R6" t="n">
-        <v>7070534</v>
+        <v>7070188</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291566</v>
+        <v>122291577</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498034</v>
+        <v>498167</v>
       </c>
       <c r="R7" t="n">
-        <v>7070179</v>
+        <v>7070254</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291573</v>
+        <v>122291583</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498343</v>
+        <v>498056</v>
       </c>
       <c r="R8" t="n">
-        <v>7070472</v>
+        <v>7070237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291581</v>
+        <v>122291585</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498055</v>
+        <v>497973</v>
       </c>
       <c r="R9" t="n">
-        <v>7070278</v>
+        <v>7070257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291582</v>
+        <v>122291567</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498057</v>
+        <v>498038</v>
       </c>
       <c r="R10" t="n">
-        <v>7070278</v>
+        <v>7070174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291565</v>
+        <v>122291572</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498003</v>
+        <v>498387</v>
       </c>
       <c r="R11" t="n">
-        <v>7070188</v>
+        <v>7070463</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291571</v>
+        <v>122291566</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498388</v>
+        <v>498034</v>
       </c>
       <c r="R12" t="n">
-        <v>7070466</v>
+        <v>7070179</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291572</v>
+        <v>122291584</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -1992,17 +1992,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498387</v>
+        <v>497959</v>
       </c>
       <c r="R14" t="n">
-        <v>7070463</v>
+        <v>7070233</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,11 +2055,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291563</v>
+        <v>122291564</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2106,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497800</v>
+        <v>497847</v>
       </c>
       <c r="R15" t="n">
-        <v>7070212</v>
+        <v>7070241</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291583</v>
+        <v>122291563</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2213,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498056</v>
+        <v>497800</v>
       </c>
       <c r="R16" t="n">
-        <v>7070237</v>
+        <v>7070212</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2268,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291580</v>
+        <v>122291575</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498114</v>
+        <v>498330</v>
       </c>
       <c r="R17" t="n">
-        <v>7070295</v>
+        <v>7070466</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291575</v>
+        <v>122291568</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2427,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498330</v>
+        <v>498247</v>
       </c>
       <c r="R18" t="n">
-        <v>7070466</v>
+        <v>7070260</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291578</v>
+        <v>122291574</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2534,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498060</v>
+        <v>498338</v>
       </c>
       <c r="R19" t="n">
-        <v>7070363</v>
+        <v>7070474</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291584</v>
+        <v>122291580</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2634,37 +2649,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497959</v>
+        <v>498114</v>
       </c>
       <c r="R20" t="n">
-        <v>7070233</v>
+        <v>7070295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,6 +2692,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291579</v>
+        <v>122291582</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498060</v>
+        <v>498057</v>
       </c>
       <c r="R21" t="n">
-        <v>7070326</v>
+        <v>7070278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291574</v>
+        <v>122291581</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498338</v>
+        <v>498055</v>
       </c>
       <c r="R22" t="n">
-        <v>7070474</v>
+        <v>7070278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291585</v>
+        <v>122291578</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497973</v>
+        <v>498060</v>
       </c>
       <c r="R23" t="n">
-        <v>7070257</v>
+        <v>7070363</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291568</v>
+        <v>122291570</v>
       </c>
       <c r="B24" t="n">
         <v>57383</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498247</v>
+        <v>498390</v>
       </c>
       <c r="R24" t="n">
-        <v>7070260</v>
+        <v>7070534</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291571</v>
+        <v>122291578</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498388</v>
+        <v>498060</v>
       </c>
       <c r="R2" t="n">
-        <v>7070466</v>
+        <v>7070363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291573</v>
+        <v>122291568</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498343</v>
+        <v>498247</v>
       </c>
       <c r="R3" t="n">
-        <v>7070472</v>
+        <v>7070260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291579</v>
+        <v>122291585</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498060</v>
+        <v>497973</v>
       </c>
       <c r="R4" t="n">
-        <v>7070326</v>
+        <v>7070257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291569</v>
+        <v>122291579</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498385</v>
+        <v>498060</v>
       </c>
       <c r="R5" t="n">
-        <v>7070568</v>
+        <v>7070326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291565</v>
+        <v>122291581</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498003</v>
+        <v>498055</v>
       </c>
       <c r="R6" t="n">
-        <v>7070188</v>
+        <v>7070278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291577</v>
+        <v>122291573</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498167</v>
+        <v>498343</v>
       </c>
       <c r="R7" t="n">
-        <v>7070254</v>
+        <v>7070472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291583</v>
+        <v>122291584</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,17 +1350,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498056</v>
+        <v>497959</v>
       </c>
       <c r="R8" t="n">
-        <v>7070237</v>
+        <v>7070233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1413,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291585</v>
+        <v>122291564</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497973</v>
+        <v>497847</v>
       </c>
       <c r="R9" t="n">
-        <v>7070257</v>
+        <v>7070241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1519,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291567</v>
+        <v>122291566</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498038</v>
+        <v>498034</v>
       </c>
       <c r="R10" t="n">
-        <v>7070174</v>
+        <v>7070179</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291572</v>
+        <v>122291577</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498387</v>
+        <v>498167</v>
       </c>
       <c r="R11" t="n">
-        <v>7070463</v>
+        <v>7070254</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291566</v>
+        <v>122291574</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498034</v>
+        <v>498338</v>
       </c>
       <c r="R12" t="n">
-        <v>7070179</v>
+        <v>7070474</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1840,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291576</v>
+        <v>122291583</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498249</v>
+        <v>498056</v>
       </c>
       <c r="R13" t="n">
-        <v>7070325</v>
+        <v>7070237</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291584</v>
+        <v>122291563</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,37 +2007,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497959</v>
+        <v>497800</v>
       </c>
       <c r="R14" t="n">
-        <v>7070233</v>
+        <v>7070212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,6 +2050,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291564</v>
+        <v>122291572</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497847</v>
+        <v>498387</v>
       </c>
       <c r="R15" t="n">
-        <v>7070241</v>
+        <v>7070463</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291563</v>
+        <v>122291570</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497800</v>
+        <v>498390</v>
       </c>
       <c r="R16" t="n">
-        <v>7070212</v>
+        <v>7070534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
         <v>122291575</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291568</v>
+        <v>122291567</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498247</v>
+        <v>498038</v>
       </c>
       <c r="R18" t="n">
-        <v>7070260</v>
+        <v>7070174</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291574</v>
+        <v>122291571</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498338</v>
+        <v>498388</v>
       </c>
       <c r="R19" t="n">
-        <v>7070474</v>
+        <v>7070466</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291580</v>
+        <v>122291576</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498114</v>
+        <v>498249</v>
       </c>
       <c r="R20" t="n">
-        <v>7070295</v>
+        <v>7070325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291582</v>
+        <v>122291580</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498057</v>
+        <v>498114</v>
       </c>
       <c r="R21" t="n">
-        <v>7070278</v>
+        <v>7070295</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291581</v>
+        <v>122291582</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498055</v>
+        <v>498057</v>
       </c>
       <c r="R22" t="n">
         <v>7070278</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291578</v>
+        <v>122291569</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498060</v>
+        <v>498385</v>
       </c>
       <c r="R23" t="n">
-        <v>7070363</v>
+        <v>7070568</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3044,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291570</v>
+        <v>122291565</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498390</v>
+        <v>498003</v>
       </c>
       <c r="R24" t="n">
-        <v>7070534</v>
+        <v>7070188</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291578</v>
+        <v>122291567</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498060</v>
+        <v>498038</v>
       </c>
       <c r="R2" t="n">
-        <v>7070363</v>
+        <v>7070174</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291568</v>
+        <v>122291570</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498247</v>
+        <v>498390</v>
       </c>
       <c r="R3" t="n">
-        <v>7070260</v>
+        <v>7070534</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291579</v>
+        <v>122291578</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1039,7 +1039,7 @@
         <v>498060</v>
       </c>
       <c r="R5" t="n">
-        <v>7070326</v>
+        <v>7070363</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291581</v>
+        <v>122291579</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498055</v>
+        <v>498060</v>
       </c>
       <c r="R6" t="n">
-        <v>7070278</v>
+        <v>7070326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291573</v>
+        <v>122291569</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498343</v>
+        <v>498385</v>
       </c>
       <c r="R7" t="n">
-        <v>7070472</v>
+        <v>7070568</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291584</v>
+        <v>122291582</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1350,37 +1350,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497959</v>
+        <v>498057</v>
       </c>
       <c r="R8" t="n">
-        <v>7070233</v>
+        <v>7070278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291564</v>
+        <v>122291563</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1479,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497847</v>
+        <v>497800</v>
       </c>
       <c r="R9" t="n">
-        <v>7070241</v>
+        <v>7070212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291566</v>
+        <v>122291575</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1586,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498034</v>
+        <v>498330</v>
       </c>
       <c r="R10" t="n">
-        <v>7070179</v>
+        <v>7070466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291577</v>
+        <v>122291581</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1693,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498167</v>
+        <v>498055</v>
       </c>
       <c r="R11" t="n">
-        <v>7070254</v>
+        <v>7070278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291574</v>
+        <v>122291573</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1800,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498338</v>
+        <v>498343</v>
       </c>
       <c r="R12" t="n">
-        <v>7070474</v>
+        <v>7070472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291583</v>
+        <v>122291576</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1907,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498056</v>
+        <v>498249</v>
       </c>
       <c r="R13" t="n">
-        <v>7070237</v>
+        <v>7070325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291563</v>
+        <v>122291564</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -2014,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497800</v>
+        <v>497847</v>
       </c>
       <c r="R14" t="n">
-        <v>7070212</v>
+        <v>7070241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291572</v>
+        <v>122291568</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2121,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498387</v>
+        <v>498247</v>
       </c>
       <c r="R15" t="n">
-        <v>7070463</v>
+        <v>7070260</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2188,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291570</v>
+        <v>122291565</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2228,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498390</v>
+        <v>498003</v>
       </c>
       <c r="R16" t="n">
-        <v>7070534</v>
+        <v>7070188</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291575</v>
+        <v>122291583</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2335,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498330</v>
+        <v>498056</v>
       </c>
       <c r="R17" t="n">
-        <v>7070466</v>
+        <v>7070237</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291567</v>
+        <v>122291574</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2442,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498038</v>
+        <v>498338</v>
       </c>
       <c r="R18" t="n">
-        <v>7070174</v>
+        <v>7070474</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291571</v>
+        <v>122291566</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2549,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498388</v>
+        <v>498034</v>
       </c>
       <c r="R19" t="n">
-        <v>7070466</v>
+        <v>7070179</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291576</v>
+        <v>122291577</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2656,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498249</v>
+        <v>498167</v>
       </c>
       <c r="R20" t="n">
-        <v>7070325</v>
+        <v>7070254</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2723,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291580</v>
+        <v>122291584</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2756,17 +2741,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498114</v>
+        <v>497959</v>
       </c>
       <c r="R21" t="n">
-        <v>7070295</v>
+        <v>7070233</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,11 +2804,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291582</v>
+        <v>122291572</v>
       </c>
       <c r="B22" t="n">
         <v>57384</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498057</v>
+        <v>498387</v>
       </c>
       <c r="R22" t="n">
-        <v>7070278</v>
+        <v>7070463</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291569</v>
+        <v>122291580</v>
       </c>
       <c r="B23" t="n">
         <v>57384</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498385</v>
+        <v>498114</v>
       </c>
       <c r="R23" t="n">
-        <v>7070568</v>
+        <v>7070295</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291565</v>
+        <v>122291571</v>
       </c>
       <c r="B24" t="n">
         <v>57384</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498003</v>
+        <v>498388</v>
       </c>
       <c r="R24" t="n">
-        <v>7070188</v>
+        <v>7070466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 53170-2024 artfynd.xlsx
+++ b/artfynd/A 53170-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122291567</v>
+        <v>122291577</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498038</v>
+        <v>498167</v>
       </c>
       <c r="R2" t="n">
-        <v>7070174</v>
+        <v>7070254</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122291570</v>
+        <v>122291569</v>
       </c>
       <c r="B3" t="n">
         <v>57384</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498390</v>
+        <v>498385</v>
       </c>
       <c r="R3" t="n">
-        <v>7070534</v>
+        <v>7070568</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122291585</v>
+        <v>122291571</v>
       </c>
       <c r="B4" t="n">
         <v>57384</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497973</v>
+        <v>498388</v>
       </c>
       <c r="R4" t="n">
-        <v>7070257</v>
+        <v>7070466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122291578</v>
+        <v>122291576</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498060</v>
+        <v>498249</v>
       </c>
       <c r="R5" t="n">
-        <v>7070363</v>
+        <v>7070325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122291579</v>
+        <v>122291582</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498060</v>
+        <v>498057</v>
       </c>
       <c r="R6" t="n">
-        <v>7070326</v>
+        <v>7070278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122291569</v>
+        <v>122291572</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498385</v>
+        <v>498387</v>
       </c>
       <c r="R7" t="n">
-        <v>7070568</v>
+        <v>7070463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122291582</v>
+        <v>122291573</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498057</v>
+        <v>498343</v>
       </c>
       <c r="R8" t="n">
-        <v>7070278</v>
+        <v>7070472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122291563</v>
+        <v>122291584</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1457,17 +1457,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497800</v>
+        <v>497959</v>
       </c>
       <c r="R9" t="n">
-        <v>7070212</v>
+        <v>7070233</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1520,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1546,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122291575</v>
+        <v>122291563</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1571,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498330</v>
+        <v>497800</v>
       </c>
       <c r="R10" t="n">
-        <v>7070466</v>
+        <v>7070212</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122291581</v>
+        <v>122291575</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1678,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498055</v>
+        <v>498330</v>
       </c>
       <c r="R11" t="n">
-        <v>7070278</v>
+        <v>7070466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1760,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122291573</v>
+        <v>122291581</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1785,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498343</v>
+        <v>498055</v>
       </c>
       <c r="R12" t="n">
-        <v>7070472</v>
+        <v>7070278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1867,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122291576</v>
+        <v>122291565</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1892,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498249</v>
+        <v>498003</v>
       </c>
       <c r="R13" t="n">
-        <v>7070325</v>
+        <v>7070188</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122291564</v>
+        <v>122291566</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -1999,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497847</v>
+        <v>498034</v>
       </c>
       <c r="R14" t="n">
-        <v>7070241</v>
+        <v>7070179</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2054,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122291568</v>
+        <v>122291570</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2106,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498247</v>
+        <v>498390</v>
       </c>
       <c r="R15" t="n">
-        <v>7070260</v>
+        <v>7070534</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2188,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122291565</v>
+        <v>122291568</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2213,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498003</v>
+        <v>498247</v>
       </c>
       <c r="R16" t="n">
-        <v>7070188</v>
+        <v>7070260</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122291583</v>
+        <v>122291574</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2320,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498056</v>
+        <v>498338</v>
       </c>
       <c r="R17" t="n">
-        <v>7070237</v>
+        <v>7070474</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122291574</v>
+        <v>122291580</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2427,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498338</v>
+        <v>498114</v>
       </c>
       <c r="R18" t="n">
-        <v>7070474</v>
+        <v>7070295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2482,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2509,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122291566</v>
+        <v>122291578</v>
       </c>
       <c r="B19" t="n">
         <v>57384</v>
@@ -2534,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498034</v>
+        <v>498060</v>
       </c>
       <c r="R19" t="n">
-        <v>7070179</v>
+        <v>7070363</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2589,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122291577</v>
+        <v>122291564</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2641,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498167</v>
+        <v>497847</v>
       </c>
       <c r="R20" t="n">
-        <v>7070254</v>
+        <v>7070241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122291584</v>
+        <v>122291567</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2741,37 +2756,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ängeskälen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497959</v>
+        <v>498038</v>
       </c>
       <c r="R21" t="n">
-        <v>7070233</v>
+        <v>7070174</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,6 +2799,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122291572</v>
+        <v>122291583</v>
       </c>
       <c r="B22" t="n">
         <v>57384</v>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498387</v>
+        <v>498056</v>
       </c>
       <c r="R22" t="n">
-        <v>7070463</v>
+        <v>7070237</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122291580</v>
+        <v>122291579</v>
       </c>
       <c r="B23" t="n">
         <v>57384</v>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498114</v>
+        <v>498060</v>
       </c>
       <c r="R23" t="n">
-        <v>7070295</v>
+        <v>7070326</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122291571</v>
+        <v>122291585</v>
       </c>
       <c r="B24" t="n">
         <v>57384</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498388</v>
+        <v>497973</v>
       </c>
       <c r="R24" t="n">
-        <v>7070466</v>
+        <v>7070257</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
